--- a/Drew_White_Husker_Football_Visualization.xlsx
+++ b/Drew_White_Husker_Football_Visualization.xlsx
@@ -54,13 +54,13 @@
     <t xml:space="preserve">Source</t>
   </si>
   <si>
-    <t xml:space="preserve">Wikipedia, 'List of Nebraska Cornhuskers football seasons' (https://en.wikipedia.org/wiki/List_of_Nebraska_Cornhuskers_football_seasons), retrieved Oct 9, 2026; table compiled from the Nebraska Athletics Football Record Book and NCAA records.</t>
+    <t xml:space="preserve">Wikipedia, 'List of Nebraska Cornhuskers football seasons' (https://en.wikipedia.org/wiki/List_of_Nebraska_Cornhuskers_football_seasons); table compiled from the Nebraska Athletics Football Record Book and NCAA records.</t>
   </si>
   <si>
     <t xml:space="preserve">Raw_Data</t>
   </si>
   <si>
-    <t xml:space="preserve">The table as retrieved: 137 rows x 9 columns, text values (records like '9–2–1', ranks like 'T–20').</t>
+    <t xml:space="preserve">The original table: 137 rows x 9 columns, text values (records like '9–2–1', ranks like 'T–20').</t>
   </si>
   <si>
     <t xml:space="preserve">Clean_Data</t>
@@ -1506,7 +1506,7 @@
     <t xml:space="preserve">Story</t>
   </si>
   <si>
-    <t xml:space="preserve">The 10-season average shows three big periods. Nebraska won a lot early on, then hit its low point in the 1940s and 50s (.337 average by 1951). After Bob Devaney was hired in 1962 the line shot up and peaked at .881 from 1992-2001. Since then it has gone down, and the 2016-2025 average (.423) is the lowest since 1962.</t>
+    <t xml:space="preserve">Nebraska won a lot early on, then hit its low point in the 1940s and 50s. After Bob Devaney was hired in 1962 the line went way up and peaked from 1992-2001 (.881). It has gone down since then, and the last 10 years (.423) are the worst since 1962.</t>
   </si>
   <si>
     <t xml:space="preserve">Goal 2: Win % by Decade</t>
@@ -1521,7 +1521,7 @@
     <t xml:space="preserve">Note: 2020s = 6 seasons (2020-2025). Ties count as half a win.</t>
   </si>
   <si>
-    <t xml:space="preserve">The 1990s were the best decade at .868, and the 70s, 80s, and 90s were all above .800. The 1940s were the worst (.374). Every decade since the 1990s has been worse than the one before it, and the 2020s are at .414 so far.</t>
+    <t xml:space="preserve">The 1990s were the best decade (.868) and the 1940s were the worst (.374). Every decade since the 1990s has been worse than the one before it.</t>
   </si>
   <si>
     <t xml:space="preserve">Goal 3: Head Coaches Since 1962</t>
@@ -1545,7 +1545,7 @@
     <t xml:space="preserve">Coaches since 1962, sorted by win %. Interim coaches credited per source table.</t>
   </si>
   <si>
-    <t xml:space="preserve">Osborne (.836) and Devaney (.829) are way ahead of everyone else. Osborne went to a bowl and finished ranked in all 25 of his seasons. Every coach since 2015 is at .500 or below, and Scott Frost (.339) is the lowest.</t>
+    <t xml:space="preserve">Osborne (.836) and Devaney (.829) are way ahead of everyone else. Every coach since 2015 is at .500 or below, and Scott Frost (.339) is last.</t>
   </si>
   <si>
     <t xml:space="preserve">Goal 4: Conference Eras</t>
@@ -1569,7 +1569,7 @@
     <t xml:space="preserve">% seasons final AP ranked</t>
   </si>
   <si>
-    <t xml:space="preserve">Every measure goes down from the Big Eight to the Big 12 to the Big Ten. The biggest drop is in rankings: 91% of Big Eight seasons ended ranked, but only 13% of Big Ten seasons did. The drop started before the Big Ten though, since the team had bad years in 2004 and 2007.</t>
+    <t xml:space="preserve">Every bar gets shorter from the Big Eight to the Big 12 to the Big Ten. The biggest drop is rankings: 91% of Big Eight seasons ended ranked, but only 13% of Big Ten seasons did.</t>
   </si>
   <si>
     <t xml:space="preserve">Goal 5: Bowl Games</t>
@@ -1593,7 +1593,7 @@
     <t xml:space="preserve">Nebraska's first bowl game was the 1941 Rose Bowl (1940 season).</t>
   </si>
   <si>
-    <t xml:space="preserve">Nebraska went to 35 bowl games in a row from 1969 to 2003, so the 70s, 80s, and 90s all have 10. The 1970s were the best at 7-3. The all-time bowl record is 27-28, but only 3-5 in the Big Ten. The team didn't go to a bowl from 2017 to 2023.</t>
+    <t xml:space="preserve">Nebraska went to 35 bowl games in a row from 1969 to 2003. Their all-time bowl record is 27-28. They didn't make a bowl from 2017 to 2023.</t>
   </si>
   <si>
     <t xml:space="preserve">Goal 6: Final AP Rankings</t>
@@ -1611,7 +1611,7 @@
     <t xml:space="preserve">Top-10 finishes</t>
   </si>
   <si>
-    <t xml:space="preserve">From 1969 to 2001 Nebraska was ranked every year (33 in a row) and finished #1 four times. After 2001 the dots drop and spread out. The last time they finished ranked was 2012 (#25), so it's been 13 seasons.</t>
+    <t xml:space="preserve">From 1969 to 2001 Nebraska was ranked every year and finished #1 four times. They haven't finished ranked since 2012.</t>
   </si>
 </sst>
 </file>
@@ -3805,11 +3805,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="35371545"/>
-        <c:axId val="35636266"/>
+        <c:axId val="20370621"/>
+        <c:axId val="2906338"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="35371545"/>
+        <c:axId val="20370621"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2030"/>
@@ -3877,13 +3877,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35636266"/>
+        <c:crossAx val="2906338"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="10"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="35636266"/>
+        <c:axId val="2906338"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3961,7 +3961,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35371545"/>
+        <c:crossAx val="20370621"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.2"/>
@@ -4219,11 +4219,11 @@
         </c:ser>
         <c:gapWidth val="40"/>
         <c:overlap val="0"/>
-        <c:axId val="45971679"/>
-        <c:axId val="60516718"/>
+        <c:axId val="68421219"/>
+        <c:axId val="63743186"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="45971679"/>
+        <c:axId val="68421219"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4289,7 +4289,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60516718"/>
+        <c:crossAx val="63743186"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4297,7 +4297,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60516718"/>
+        <c:axId val="63743186"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4375,7 +4375,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45971679"/>
+        <c:crossAx val="68421219"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4572,11 +4572,11 @@
         </c:ser>
         <c:gapWidth val="35"/>
         <c:overlap val="0"/>
-        <c:axId val="62949568"/>
-        <c:axId val="59123275"/>
+        <c:axId val="56551816"/>
+        <c:axId val="66918445"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="62949568"/>
+        <c:axId val="56551816"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4608,7 +4608,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59123275"/>
+        <c:crossAx val="66918445"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4616,7 +4616,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59123275"/>
+        <c:axId val="66918445"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4694,7 +4694,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62949568"/>
+        <c:crossAx val="56551816"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5137,11 +5137,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="63359877"/>
-        <c:axId val="44896287"/>
+        <c:axId val="10458409"/>
+        <c:axId val="94246485"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="63359877"/>
+        <c:axId val="10458409"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5173,7 +5173,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44896287"/>
+        <c:crossAx val="94246485"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5181,7 +5181,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44896287"/>
+        <c:axId val="94246485"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -5259,7 +5259,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63359877"/>
+        <c:crossAx val="10458409"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5612,11 +5612,11 @@
         </c:ser>
         <c:gapWidth val="50"/>
         <c:overlap val="100"/>
-        <c:axId val="81864132"/>
-        <c:axId val="99540653"/>
+        <c:axId val="85626965"/>
+        <c:axId val="1325256"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="81864132"/>
+        <c:axId val="85626965"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5682,7 +5682,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99540653"/>
+        <c:crossAx val="1325256"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5690,7 +5690,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99540653"/>
+        <c:axId val="1325256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -5768,7 +5768,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81864132"/>
+        <c:crossAx val="85626965"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>
@@ -6229,11 +6229,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="65453147"/>
-        <c:axId val="33411217"/>
+        <c:axId val="12465811"/>
+        <c:axId val="9983670"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="65453147"/>
+        <c:axId val="12465811"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2030"/>
@@ -6301,13 +6301,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33411217"/>
+        <c:crossAx val="9983670"/>
         <c:crosses val="max"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="10"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="33411217"/>
+        <c:axId val="9983670"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
           <c:max val="25"/>
@@ -6385,7 +6385,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65453147"/>
+        <c:crossAx val="12465811"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="4"/>
